--- a/student_under_hod.xlsx
+++ b/student_under_hod.xlsx
@@ -507,7 +507,7 @@
         <v>8449514087</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
         <v>34</v>
@@ -550,7 +550,7 @@
         <v>8307200447</v>
       </c>
       <c r="I3" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
         <v>32</v>
@@ -593,7 +593,7 @@
         <v>8449514087</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="J4" t="n">
         <v>45</v>
@@ -636,7 +636,7 @@
         <v>8449512048</v>
       </c>
       <c r="I5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J5" t="n">
         <v>100</v>
@@ -679,7 +679,7 @@
         <v>8307200447</v>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J6" t="n">
         <v>100</v>
